--- a/data/carl_demo_requests.xlsx
+++ b/data/carl_demo_requests.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -904,10 +904,113 @@
           <t>Navale IT Zone</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>192.168.1.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-04-09 01:57:31 UTC</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Gaurav</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>pune</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>gaurav@ieng.tech</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>PH</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>+63</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>+634-02040</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>192.168.1.51</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-04-09 02:12:37 UTC</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Gaurav</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>iEng</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>gaurav@ieng.tech</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>PH</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>+63</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>+634-02040</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>pune</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Ieng</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>192.168.1.51</t>
         </is>
       </c>
     </row>
